--- a/Generate Files/BOM/243-436_MP_Man-ESP32.xlsx
+++ b/Generate Files/BOM/243-436_MP_Man-ESP32.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/243-436 - Developpement de produits 4 - Dessins et Certifications/laboratoires/Labo 2 - MP-ManCtrl-ESP32-PCB/Generate Files/BOM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/243-436-Dev-Prod4-Certifications/laboratoires/Labo3-ContoleurManette-ESP32/243-436-ManCtrl-ESP32/Generate Files/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33DD27A1-4FC1-45E7-8419-4993346EED9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA75D52A-D873-4150-B06C-A27C229B7BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="600" windowWidth="20052" windowHeight="11592" xr2:uid="{6B331DCA-BFA7-467C-AFA7-29FE570D8C4C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E34C461-4169-4AAC-8733-B4427D8019C3}"/>
   </bookViews>
   <sheets>
     <sheet name="243-436_MP_Man-ESP32" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="123">
   <si>
     <t>LibRef</t>
   </si>
@@ -119,7 +119,7 @@
     <t>Code CEGEP</t>
   </si>
   <si>
-    <t>CMP-12798-000012-1</t>
+    <t>Q_BC847BW</t>
   </si>
   <si>
     <t>BC847BW-7-F</t>
@@ -131,259 +131,244 @@
     <t>Q1, Q2</t>
   </si>
   <si>
-    <t>Diodes Inc.</t>
-  </si>
-  <si>
-    <t>Farnell</t>
-  </si>
-  <si>
-    <t>1773619</t>
+    <t>Diodes Inc</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CAP001</t>
+  </si>
+  <si>
+    <t>CAP CER 100nF 50V 0402</t>
+  </si>
+  <si>
+    <t>Capacitor type 1</t>
+  </si>
+  <si>
+    <t>C3, C5, C8, C9</t>
+  </si>
+  <si>
+    <t>Yageo</t>
+  </si>
+  <si>
+    <t>CC0402KRX7R9BB104</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>C131394</t>
+  </si>
+  <si>
+    <t>SMT</t>
+  </si>
+  <si>
+    <t>KCOND01SM</t>
+  </si>
+  <si>
+    <t>CAP016</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7uF 6.3V X5R 0402</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>Samsung Electro-Mechanics</t>
+  </si>
+  <si>
+    <t>CL05A475MQ5NRNC</t>
+  </si>
+  <si>
+    <t>C307423</t>
   </si>
   <si>
     <t>CAD</t>
   </si>
   <si>
-    <t>1773619RL</t>
-  </si>
-  <si>
-    <t>U_ESP32-WROOM-32E-N4</t>
+    <t>CAP020</t>
+  </si>
+  <si>
+    <t>CAP CER 10uF 25V X5R 0805</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>CL21A106KAYNNNE</t>
+  </si>
+  <si>
+    <t>C15850</t>
+  </si>
+  <si>
+    <t>J_Conn_02x05</t>
+  </si>
+  <si>
+    <t>HC-PBB12NB(3.0)-10DS-0.5V-03</t>
+  </si>
+  <si>
+    <t>Connector Receptacle 2x5pos, 0,5mm</t>
+  </si>
+  <si>
+    <t>J1, J2</t>
+  </si>
+  <si>
+    <t>HRS</t>
+  </si>
+  <si>
+    <t>DF12NB(3.0)-10DS-0.5V(51)</t>
+  </si>
+  <si>
+    <t>HIROSE ELECTRIC</t>
+  </si>
+  <si>
+    <t>C2904118</t>
+  </si>
+  <si>
+    <t>DigiKey</t>
+  </si>
+  <si>
+    <t>26-DF12NB(3.0)-10DS-0.5V(51)CT-ND</t>
+  </si>
+  <si>
+    <t>KPTSO011</t>
+  </si>
+  <si>
+    <t>RES003</t>
+  </si>
+  <si>
+    <t>Res 10k 1% 0402</t>
+  </si>
+  <si>
+    <t>Resistor type 1</t>
+  </si>
+  <si>
+    <t>R1, R2, R7, R8, R9, R10, R13, R14</t>
+  </si>
+  <si>
+    <t>RC0402FR-0710KL</t>
+  </si>
+  <si>
+    <t>C60490</t>
+  </si>
+  <si>
+    <t>RES005</t>
+  </si>
+  <si>
+    <t>Res 0R 0402</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>RC0402JR-070RL</t>
+  </si>
+  <si>
+    <t>C60485</t>
+  </si>
+  <si>
+    <t>RES0SM</t>
+  </si>
+  <si>
+    <t>RES006</t>
+  </si>
+  <si>
+    <t>Res 1k 1% 0402</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>RC0402FR-071kL</t>
+  </si>
+  <si>
+    <t>C106235</t>
+  </si>
+  <si>
+    <t>RES1KSM</t>
+  </si>
+  <si>
+    <t>RES007</t>
+  </si>
+  <si>
+    <t>Res 4k7 1% 0402</t>
+  </si>
+  <si>
+    <t>R11, R12, R16</t>
+  </si>
+  <si>
+    <t>RC0402FR-074K7L</t>
+  </si>
+  <si>
+    <t>C105871</t>
+  </si>
+  <si>
+    <t>RES4.7KSM</t>
+  </si>
+  <si>
+    <t>SW_B3U-1000P</t>
+  </si>
+  <si>
+    <t>HX-B3U-1000P-1.6N</t>
+  </si>
+  <si>
+    <t>SWITCH TACTILE SPST-NO 0.05A 12V</t>
+  </si>
+  <si>
+    <t>BOOT, RST</t>
+  </si>
+  <si>
+    <t>hanxia</t>
+  </si>
+  <si>
+    <t>Omron</t>
+  </si>
+  <si>
+    <t>B3U-1000P</t>
+  </si>
+  <si>
+    <t>C49234121</t>
+  </si>
+  <si>
+    <t>U_CH340X</t>
+  </si>
+  <si>
+    <t>CH340X</t>
+  </si>
+  <si>
+    <t>IC USB to Serial Port</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>WCH(Jiangsu Qin Heng)</t>
+  </si>
+  <si>
+    <t>C3035748</t>
+  </si>
+  <si>
+    <t>M_ESP32-WROOM-32E-N4-TH</t>
   </si>
   <si>
     <t>ESP32-WROOM-32E-N4</t>
   </si>
   <si>
-    <t>U1</t>
+    <t>ESP32 Module SMT Castellated</t>
+  </si>
+  <si>
+    <t>M1</t>
   </si>
   <si>
     <t>Espressif Systems</t>
   </si>
   <si>
-    <t>LCSC</t>
-  </si>
-  <si>
     <t>C701341</t>
   </si>
   <si>
-    <t>CAP001</t>
-  </si>
-  <si>
-    <t>CAP CER 100nF 50V 0402</t>
-  </si>
-  <si>
-    <t>Capacitor type 1</t>
-  </si>
-  <si>
-    <t>C3, C4, C5, C8, C9</t>
-  </si>
-  <si>
-    <t>TAIYO YUDEN</t>
-  </si>
-  <si>
-    <t>UMK105B7104KV-FR</t>
-  </si>
-  <si>
-    <t>C2167491</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>SMT</t>
-  </si>
-  <si>
-    <t>KCOND01SM</t>
-  </si>
-  <si>
-    <t>CAP016</t>
-  </si>
-  <si>
-    <t>CAP CER 4.7uF 6.3V X5R 0402</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>Samsung Electro-Mechanics</t>
-  </si>
-  <si>
-    <t>CL05A475MQ5NRNC</t>
-  </si>
-  <si>
-    <t>C307423</t>
-  </si>
-  <si>
-    <t>CAP020</t>
-  </si>
-  <si>
-    <t>CAP CER 10uF 25V X5R 0805</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>Murata</t>
-  </si>
-  <si>
-    <t>GRM21BR71A106KE51L</t>
-  </si>
-  <si>
-    <t>C86038</t>
-  </si>
-  <si>
-    <t>J_Conn_02x05</t>
-  </si>
-  <si>
-    <t>HC-PBB12NB(3.0)-10DS-0.5V-03</t>
-  </si>
-  <si>
-    <t>Connector Receptacle 2x5pos, 0,5mm</t>
-  </si>
-  <si>
-    <t>J1, J2</t>
-  </si>
-  <si>
-    <t>HRS</t>
-  </si>
-  <si>
-    <t>DF12NB(3.0)-10DS-0.5V(51)</t>
-  </si>
-  <si>
-    <t>HIROSE ELECTRIC</t>
-  </si>
-  <si>
-    <t>C2904118</t>
-  </si>
-  <si>
-    <t>DigiKey</t>
-  </si>
-  <si>
-    <t>26-DF12NB(3.0)-10DS-0.5V(51)CT-ND</t>
-  </si>
-  <si>
-    <t>KPTSO011</t>
-  </si>
-  <si>
-    <t>RES003</t>
-  </si>
-  <si>
-    <t>Res 10k 1% 0402</t>
-  </si>
-  <si>
-    <t>Resistor type 1</t>
-  </si>
-  <si>
-    <t>R1, R2, R3, R7, R8, R9, R10, R13, R14</t>
-  </si>
-  <si>
-    <t>Vishay</t>
-  </si>
-  <si>
-    <t>CRCW040210K0FKED</t>
-  </si>
-  <si>
-    <t>541-10.0KLCT-ND</t>
-  </si>
-  <si>
-    <t>RES005</t>
-  </si>
-  <si>
-    <t>Res 0R 0402</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>Yageo</t>
-  </si>
-  <si>
-    <t>RC0402JR-070RL</t>
-  </si>
-  <si>
-    <t>C60485</t>
-  </si>
-  <si>
-    <t>RES0SM</t>
-  </si>
-  <si>
-    <t>RES006</t>
-  </si>
-  <si>
-    <t>Res 1k 1% 0402</t>
-  </si>
-  <si>
-    <t>R15</t>
-  </si>
-  <si>
-    <t>RC0402FR-071kL</t>
-  </si>
-  <si>
-    <t>C106235</t>
-  </si>
-  <si>
-    <t>RES1KSM</t>
-  </si>
-  <si>
-    <t>RES007</t>
-  </si>
-  <si>
-    <t>Res 4k7 1% 0402</t>
-  </si>
-  <si>
-    <t>R11, R12, R16</t>
-  </si>
-  <si>
-    <t>Panasonic</t>
-  </si>
-  <si>
-    <t>ERJ-2RKF4701X</t>
-  </si>
-  <si>
-    <t>C400631</t>
-  </si>
-  <si>
-    <t>RES4.7KSM</t>
-  </si>
-  <si>
-    <t>S_B3U-1000P</t>
-  </si>
-  <si>
-    <t>HX-B3U-1000P-1.6N</t>
-  </si>
-  <si>
-    <t>SWITCH TACTILE SPST-NO 0.05A 12V</t>
-  </si>
-  <si>
-    <t>BOOT, RST</t>
-  </si>
-  <si>
-    <t>hanxia</t>
-  </si>
-  <si>
-    <t>Omron</t>
-  </si>
-  <si>
-    <t>B3U-1000P</t>
-  </si>
-  <si>
-    <t>C49234121</t>
-  </si>
-  <si>
-    <t>U_CH340X</t>
-  </si>
-  <si>
-    <t>CH340X</t>
-  </si>
-  <si>
-    <t>IC USB to Serial Port</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>WCH(Jiangsu Qin Heng)</t>
-  </si>
-  <si>
-    <t>C3035748</t>
+    <t>TH</t>
   </si>
   <si>
     <t>P_CONN-SKT-2POS-50MIL</t>
@@ -818,7 +803,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75685BCB-C22A-4DAF-8ED8-40D7C5EA1821}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83F5C18D-65AA-47A5-97B0-9B415A13F696}">
   <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -944,88 +929,60 @@
         <v>27</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="1">
-        <v>0.26051000000000002</v>
-      </c>
-      <c r="P2" s="1">
-        <v>5.21</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T2" s="1">
-        <v>7.0580000000000004E-2</v>
-      </c>
-      <c r="U2" s="1">
-        <v>1083</v>
-      </c>
-      <c r="V2" s="1">
-        <v>35.29</v>
-      </c>
-      <c r="W2" s="1">
-        <v>1083</v>
-      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -1037,22 +994,26 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
+      <c r="X3" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
+      <c r="Z3" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>44</v>
@@ -1068,328 +1029,298 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>47</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="O4" s="1">
-        <v>1.244E-2</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="P4" s="1">
-        <v>1.24</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>0.24004</v>
+      </c>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1">
-        <v>100</v>
+        <v>1684950</v>
       </c>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>50</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="O5" s="1">
-        <v>4.5199999999999997E-3</v>
+        <v>2.7980000000000001E-2</v>
       </c>
       <c r="P5" s="1">
-        <v>0.22619</v>
+        <v>0.55962999999999996</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1">
-        <v>3970850</v>
+        <v>53160</v>
       </c>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0.71050999999999997</v>
+      </c>
+      <c r="P6" s="1">
+        <v>14.21</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="1">
-        <v>4.0960000000000003E-2</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0.81927000000000005</v>
-      </c>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
+      <c r="R6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0.54152999999999996</v>
+      </c>
       <c r="U6" s="1">
-        <v>105060</v>
-      </c>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
+        <v>3556</v>
+      </c>
+      <c r="V6" s="1">
+        <v>10.83</v>
+      </c>
+      <c r="W6" s="1">
+        <v>5140</v>
+      </c>
       <c r="X6" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
+      <c r="Z6" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
       <c r="L7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0.68547999999999998</v>
-      </c>
-      <c r="P7" s="1">
-        <v>13.71</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="T7" s="1">
-        <v>6.1080000000000002E-2</v>
-      </c>
-      <c r="U7" s="1">
-        <v>2281</v>
-      </c>
-      <c r="V7" s="1">
-        <v>1.22</v>
-      </c>
-      <c r="W7" s="1">
-        <v>10197</v>
-      </c>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
       <c r="X7" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Y7" s="1"/>
-      <c r="Z7" s="2" t="s">
-        <v>73</v>
-      </c>
+      <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="1">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="2" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O8" s="1">
-        <v>2.0410000000000001E-2</v>
-      </c>
-      <c r="P8" s="1">
-        <v>2.04</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
-      <c r="U8" s="1">
-        <v>6512946</v>
-      </c>
+      <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Y8" s="1"/>
       <c r="Z8" s="2" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1402,44 +1333,44 @@
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z9" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C10" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -1452,112 +1383,106 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z10" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="1">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="J11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" s="1">
-        <v>7.0699999999999999E-3</v>
-      </c>
-      <c r="P11" s="1">
-        <v>0.70720000000000005</v>
-      </c>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
       <c r="Q11" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="1">
-        <v>116100</v>
-      </c>
+      <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y11" s="2" t="s">
-        <v>100</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Y11" s="1"/>
       <c r="Z11" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="1">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>107</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -1570,44 +1495,42 @@
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Y12" s="1"/>
-      <c r="Z12" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1620,133 +1543,133 @@
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="2" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C14" s="1">
         <v>2</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="O14" s="1">
-        <v>8.0790000000000001E-2</v>
+        <v>0.13825999999999999</v>
       </c>
       <c r="P14" s="1">
-        <v>1.62</v>
+        <v>2.77</v>
       </c>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1">
-        <v>530</v>
+        <v>1945</v>
       </c>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="Y14" s="1"/>
       <c r="Z14" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C15" s="1">
         <v>2</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="O15" s="1">
-        <v>3.1179999999999999E-2</v>
+        <v>0.28721999999999998</v>
       </c>
       <c r="P15" s="1">
-        <v>0.62353999999999998</v>
+        <v>5.74</v>
       </c>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1">
-        <v>1518</v>
+        <v>1199</v>
       </c>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="Y15" s="1"/>
       <c r="Z15" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
